--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
         <v>1.46</v>
@@ -872,7 +872,7 @@
         <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -863,7 +863,7 @@
         <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G2" t="n">
         <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,16 +875,16 @@
         <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -893,184 +893,184 @@
         <v>1.78</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,1023 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RSB Berkane</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yacoub El Mansour</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,7 +893,7 @@
         <v>1.78</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -902,7 +902,7 @@
         <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -923,7 +923,7 @@
         <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
@@ -965,28 +965,28 @@
         <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
         <v>7.4</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
         <v>9.4</v>
@@ -1007,34 +1007,34 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
@@ -1052,25 +1052,25 @@
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1434,7 +1434,7 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1443,25 +1443,25 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1476,7 +1476,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.01</v>
@@ -1488,7 +1488,7 @@
         <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>1.01</v>
@@ -1497,19 +1497,19 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1781,68 +1781,68 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,2516 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Eskilsminne</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FC Trollhattan</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>1.04</v>
       </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.24</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="S7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vasalunds IF</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="S8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gefle</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FC Stockholm Internazionale</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Trelleborgs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rosengard</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hammarby TFF</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FC Jarfalla</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jonkopings Sodra</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lunds BK</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tvaakers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Angelholms</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FC Arlanda</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sollentuna FF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FBK Karlstad</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.18</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-16 09:06:36</t>
+      <c r="R15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,7 +935,7 @@
         <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -971,10 +971,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>7.4</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
         <v>9.4</v>
@@ -1007,22 +1007,22 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1040,7 +1040,7 @@
         <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BP2" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="H3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.75</v>
       </c>
-      <c r="I3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1365,91 +1365,91 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
         <v>8.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
         <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1458,7 +1458,7 @@
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1467,128 +1467,128 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.74</v>
       </c>
-      <c r="I5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.76</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1646,203 +1646,203 @@
         <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
         <v>2.28</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>16.5</v>
+        <v>2.1</v>
       </c>
       <c r="BR5" t="n">
         <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="BT5" t="n">
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>1.48</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>310</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BU6" t="n">
         <v>2.92</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="BV6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA6" t="n">
         <v>2.32</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
         <v>1.15</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Skovde Aik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2405,34 +2405,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2626,28 +2626,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,31 +2659,31 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
         <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2880,28 +2880,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,34 +3421,34 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.02</v>
       </c>
-      <c r="K13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3891,27 +3891,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -4145,244 +4145,498 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FC Arlanda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:41:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>14:30:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Sollentuna FF</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>FBK Karlstad</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="F16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.19</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="P16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.24</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>1.19</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>1.11</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1.11</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V16" t="n">
         <v>1.02</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-06-16 11:17:21</t>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -887,22 +887,22 @@
         <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -923,10 +923,10 @@
         <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>40</v>
@@ -935,7 +935,7 @@
         <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -965,22 +965,22 @@
         <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>4.5</v>
@@ -989,7 +989,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -998,13 +998,13 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
         <v>4.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
@@ -1126,7 +1126,7 @@
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -1141,7 +1141,7 @@
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
@@ -1156,7 +1156,7 @@
         <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
         <v>1.19</v>
@@ -1168,7 +1168,7 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>55</v>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>4.6</v>
@@ -1398,13 +1398,13 @@
         <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>2.08</v>
@@ -1413,7 +1413,7 @@
         <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
         <v>2.2</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1485,7 +1485,7 @@
         <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AU4" t="n">
         <v>3.05</v>
@@ -1497,10 +1497,10 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>3.85</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>2.74</v>
@@ -1655,7 +1655,7 @@
         <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1664,13 +1664,13 @@
         <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1682,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1694,7 +1694,7 @@
         <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
         <v>18.5</v>
@@ -1712,10 +1712,10 @@
         <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>170</v>
@@ -1727,64 +1727,64 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
         <v>5</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BE5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1882,22 +1882,22 @@
         <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
@@ -1906,7 +1906,7 @@
         <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
@@ -1918,10 +1918,10 @@
         <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1939,7 +1939,7 @@
         <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
@@ -1951,7 +1951,7 @@
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="n">
         <v>950</v>
@@ -1966,7 +1966,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AL6" t="n">
         <v>260</v>
@@ -1984,13 +1984,13 @@
         <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT6" t="n">
         <v>4.7</v>
@@ -2002,34 +2002,34 @@
         <v>3.85</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
         <v>3.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.15</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
         <v>1.19</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H12" t="n">
         <v>1.1</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3917,218 +3917,218 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4177,212 +4177,212 @@
         <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -980,7 +980,7 @@
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>4.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
@@ -1126,7 +1126,7 @@
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -1153,7 +1153,7 @@
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
         <v>1.73</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1670,19 +1670,19 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
         <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1706,7 +1706,7 @@
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
         <v>48</v>
@@ -1724,61 +1724,61 @@
         <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.96</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="I6" t="n">
         <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1924,7 +1924,7 @@
         <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.15</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2928,7 +2928,7 @@
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G12" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,19 +3421,19 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.33</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
         <v>1.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
         <v>1.1</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O15" t="n">
         <v>1.11</v>
@@ -4207,10 +4207,10 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -4452,7 +4452,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
         <v>9</v>
@@ -884,25 +884,25 @@
         <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -965,25 +965,25 @@
         <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
         <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -1004,43 +1004,43 @@
         <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
         <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
         <v>5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP2" t="n">
         <v>8.6</v>
@@ -1052,25 +1052,25 @@
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -1144,7 +1144,7 @@
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1153,7 +1153,7 @@
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
         <v>1.73</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
         <v>2.08</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
         <v>2.74</v>
@@ -1670,7 +1670,7 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1682,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1715,7 +1715,7 @@
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>170</v>
@@ -1724,22 +1724,22 @@
         <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ5" t="n">
         <v>3.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
         <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU5" t="n">
         <v>3.2</v>
@@ -1754,7 +1754,7 @@
         <v>4.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ5" t="n">
         <v>4.3</v>
@@ -1763,13 +1763,13 @@
         <v>4.9</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
         <v>5.1</v>
@@ -1784,7 +1784,7 @@
         <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="BN6" t="n">
         <v>14</v>
@@ -2062,19 +2062,19 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="BT6" t="n">
         <v>3.65</v>
       </c>
       <c r="BU6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BV6" t="n">
         <v>9.4</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2429,7 +2429,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
         <v>1.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2662,19 +2662,19 @@
         <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
         <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.18</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.16</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,16 +3675,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
         <v>1.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4198,7 +4198,7 @@
         <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4413,20 +4413,20 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.1</v>
       </c>
-      <c r="G16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.09</v>
-      </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.34</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.19</v>
@@ -4452,7 +4452,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -860,19 +860,19 @@
         <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -887,10 +887,10 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -899,10 +899,10 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -947,7 +947,7 @@
         <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
@@ -962,31 +962,31 @@
         <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
         <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
         <v>10.5</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1028,7 +1028,7 @@
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
@@ -1126,25 +1126,25 @@
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1159,10 +1159,10 @@
         <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1204,7 +1204,7 @@
         <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1527,10 +1527,10 @@
         <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.07</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.74</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1676,13 +1676,13 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1691,7 +1691,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
         <v>50</v>
@@ -1712,7 +1712,7 @@
         <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1724,73 +1724,73 @@
         <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
         <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>5.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP5" t="n">
         <v>23</v>
@@ -1820,7 +1820,7 @@
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
@@ -2160,7 +2160,7 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,7 +2429,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q13" t="n">
         <v>1.18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O14" t="n">
         <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q14" t="n">
         <v>1.24</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4210,7 +4210,7 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>FC Meshakhte Tkibuli</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.34</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.34</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1356,94 +1356,94 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>1.06</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1452,7 +1452,7 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
@@ -1461,7 +1461,7 @@
         <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1473,122 +1473,122 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT4" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AU4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC5" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BD5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BE5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BF5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH5" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.4</v>
+        <v>1.18</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.28</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="BR5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB6" t="n">
         <v>9</v>
       </c>
-      <c r="G6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="BF6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>11</v>
       </c>
-      <c r="AD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>300</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="BK6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>2.94</v>
-      </c>
       <c r="BV6" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.1</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Skovde Aik</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,34 +2405,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2626,22 +2626,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2683,10 +2683,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2880,22 +2880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3134,55 +3134,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.1</v>
       </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="P11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3388,55 +3388,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.1</v>
       </c>
-      <c r="G12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3642,22 +3642,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3896,28 +3896,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Skovde Aik</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3953,10 +3953,10 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4145,34 +4145,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.1</v>
       </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.17</v>
-      </c>
       <c r="K15" t="n">
         <v>1000</v>
       </c>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
         <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4399,27 +4399,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,1023 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FC Arlanda</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:29:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sollentuna FF</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FBK Karlstad</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:29:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:29:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OHiggins</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
         <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1431,10 +1431,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC4" t="n">
         <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1443,7 +1443,7 @@
         <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1455,13 +1455,13 @@
         <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
         <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AV4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1646,7 +1646,7 @@
         <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.65</v>
@@ -1664,28 +1664,28 @@
         <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>970</v>
@@ -1727,70 +1727,70 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV5" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AW5" t="n">
         <v>3.6</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>3.15</v>
       </c>
-      <c r="AY5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE5" t="n">
         <v>3.65</v>
       </c>
-      <c r="BC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,13 +1802,13 @@
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,13 +1820,13 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1885,218 +1885,218 @@
         <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>11</v>
-      </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
         <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AW6" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AX6" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AZ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BN6" t="n">
         <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
         <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2133,46 +2133,46 @@
         <v>11.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J7" t="n">
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
         <v>3</v>
@@ -2202,139 +2202,139 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
         <v>120</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AK7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AM7" t="n">
         <v>290</v>
       </c>
-      <c r="AL7" t="n">
-        <v>250</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>330</v>
-      </c>
       <c r="AN7" t="n">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="AO7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>3.95</v>
       </c>
-      <c r="AW7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BH7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BU7" t="n">
         <v>2.94</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.34</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3170,19 +3170,19 @@
         <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
         <v>1.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3424,13 +3424,13 @@
         <v>1.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
         <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4948,19 +4948,19 @@
         <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
         <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="R18" t="n">
         <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5178,22 +5178,22 @@
         <v>1.98</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
         <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -5202,13 +5202,13 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
         <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
@@ -5217,7 +5217,7 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
         <v>1.96</v>
@@ -5226,7 +5226,7 @@
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5241,7 +5241,7 @@
         <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -5253,7 +5253,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -5265,7 +5265,7 @@
         <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
         <v>29</v>
@@ -5289,10 +5289,10 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -5304,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5313,92 +5313,92 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="BR19" t="n">
         <v>44</v>
       </c>
       <c r="BS19" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV19" t="n">
         <v>50</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -5471,7 +5471,7 @@
         <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U20" t="n">
         <v>2.02</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -860,16 +860,16 @@
         <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
         <v>5.2</v>
@@ -908,7 +908,7 @@
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -923,10 +923,10 @@
         <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
         <v>40</v>
@@ -935,10 +935,10 @@
         <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>32</v>
@@ -947,19 +947,19 @@
         <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>250</v>
@@ -971,10 +971,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>10.5</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1040,7 +1040,7 @@
         <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
         <v>8.6</v>
@@ -1061,7 +1061,7 @@
         <v>9.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW2" t="n">
         <v>13.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
@@ -1150,16 +1150,16 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1389,49 +1389,49 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
         <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1440,7 +1440,7 @@
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,13 +1452,13 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.8</v>
+        <v>1.99</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.76</v>
+        <v>1.97</v>
       </c>
       <c r="AX4" t="n">
         <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.76</v>
+        <v>1.98</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
         <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1727,64 +1727,64 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="AT5" t="n">
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1876,169 +1876,169 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
         <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
@@ -2050,22 +2050,22 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
         <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
         <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS6" t="n">
         <v>8</v>
@@ -2077,26 +2077,26 @@
         <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA6" t="n">
         <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>11.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I7" t="n">
         <v>1.49</v>
@@ -2142,7 +2142,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
@@ -2154,7 +2154,7 @@
         <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
         <v>1.81</v>
@@ -2163,7 +2163,7 @@
         <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
         <v>3.35</v>
@@ -2178,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -2226,7 +2226,7 @@
         <v>220</v>
       </c>
       <c r="AM7" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN7" t="n">
         <v>480</v>
@@ -2241,7 +2241,7 @@
         <v>3.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS7" t="n">
         <v>4.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.78</v>
@@ -2420,13 +2420,13 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2910,7 +2910,7 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
         <v>1.34</v>
@@ -2925,7 +2925,7 @@
         <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3164,25 +3164,25 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="S11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3926,16 +3926,16 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
         <v>1.22</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3953,7 +3953,7 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4180,22 +4180,22 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O15" t="n">
         <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
         <v>1.15</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4434,22 +4434,22 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q16" t="n">
         <v>1.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
         <v>1.22</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
         <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -5202,7 +5202,7 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
         <v>1.78</v>
@@ -5217,10 +5217,10 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
         <v>1.28</v>
@@ -5250,7 +5250,7 @@
         <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
         <v>14.5</v>
@@ -5259,7 +5259,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>85</v>
@@ -5271,7 +5271,7 @@
         <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
@@ -5289,10 +5289,10 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -5304,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5313,28 +5313,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5364,7 +5364,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BR19" t="n">
         <v>44</v>
@@ -5376,7 +5376,7 @@
         <v>7.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV19" t="n">
         <v>50</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
         <v>4.4</v>
@@ -5447,7 +5447,7 @@
         <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -5471,7 +5471,7 @@
         <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
         <v>2.02</v>
@@ -5525,7 +5525,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>130</v>
@@ -5534,19 +5534,19 @@
         <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -5555,58 +5555,58 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AZ20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB20" t="n">
         <v>8</v>
       </c>
-      <c r="BA20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BF20" t="n">
         <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BJ20" t="n">
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
@@ -5615,10 +5615,10 @@
         <v>3.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BR20" t="n">
         <v>38</v>
@@ -5645,14 +5645,14 @@
         <v>1.93</v>
       </c>
       <c r="BZ20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -887,10 +887,10 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -908,7 +908,7 @@
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -926,7 +926,7 @@
         <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>40</v>
@@ -947,19 +947,19 @@
         <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
         <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO2" t="n">
         <v>250</v>
@@ -968,13 +968,13 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,40 +995,40 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,7 +1046,7 @@
         <v>8.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
         <v>25</v>
@@ -1058,10 +1058,10 @@
         <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BV2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>13.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,7 +1159,7 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
         <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
         <v>2.98</v>
@@ -1398,19 +1398,19 @@
         <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
         <v>1.14</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1458,7 +1458,7 @@
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1473,122 +1473,122 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="BC4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BN4" t="n">
         <v>4</v>
       </c>
-      <c r="AV4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BO4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,34 +1643,34 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,7 +1679,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1709,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.54</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.2</v>
+        <v>1.11</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.9</v>
+        <v>1.11</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>1.12</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1885,10 +1885,10 @@
         <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1897,7 +1897,7 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1909,28 +1909,28 @@
         <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
         <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
         <v>23</v>
@@ -1939,7 +1939,7 @@
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
@@ -1951,7 +1951,7 @@
         <v>46</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1981,58 +1981,58 @@
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6" t="n">
         <v>4.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA6" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7</v>
-      </c>
       <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.1</v>
@@ -2080,7 +2080,7 @@
         <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="BX6" t="n">
         <v>46</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
         <v>1.41</v>
@@ -2139,10 +2139,10 @@
         <v>1.49</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>1.41</v>
@@ -2151,7 +2151,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
@@ -2163,7 +2163,7 @@
         <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
         <v>3.35</v>
@@ -2181,28 +2181,28 @@
         <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AF7" t="n">
         <v>120</v>
@@ -2211,7 +2211,7 @@
         <v>46</v>
       </c>
       <c r="AH7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
@@ -2226,67 +2226,67 @@
         <v>220</v>
       </c>
       <c r="AM7" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN7" t="n">
         <v>480</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AZ7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.45</v>
@@ -2328,7 +2328,7 @@
         <v>3.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BV7" t="n">
         <v>9.199999999999999</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2402,16 +2402,16 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.78</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
@@ -2925,7 +2925,7 @@
         <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,19 +3167,19 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
         <v>1.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
         <v>1.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
         <v>1.18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,7 +3929,7 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4183,19 +4183,19 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
         <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
         <v>1.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>1.15</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4437,22 +4437,22 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Q16" t="n">
         <v>1.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q18" t="n">
         <v>1.21</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
@@ -5214,127 +5214,127 @@
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
         <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>15</v>
       </c>
-      <c r="AW19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>13</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5343,62 +5343,62 @@
         <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>11</v>
-      </c>
       <c r="BX19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
         <v>12</v>
       </c>
       <c r="BZ19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
         <v>10.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G20" t="n">
         <v>1.99</v>
@@ -5441,10 +5441,10 @@
         <v>4.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.4</v>
@@ -5453,25 +5453,25 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.34</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
         <v>2.02</v>
@@ -5483,34 +5483,34 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
         <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA20" t="n">
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
         <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>970</v>
@@ -5519,34 +5519,34 @@
         <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
         <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
         <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS20" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.38</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -5555,58 +5555,58 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
         <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BJ20" t="n">
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
@@ -5615,10 +5615,10 @@
         <v>3.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BR20" t="n">
         <v>38</v>
@@ -5645,14 +5645,14 @@
         <v>1.93</v>
       </c>
       <c r="BZ20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -863,19 +863,19 @@
         <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -890,16 +890,16 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
         <v>1.86</v>
@@ -911,7 +911,7 @@
         <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
         <v>34</v>
@@ -923,7 +923,7 @@
         <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>13</v>
@@ -968,37 +968,37 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
@@ -1046,13 +1046,13 @@
         <v>8.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
@@ -1061,16 +1061,16 @@
         <v>7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>970</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>32</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
@@ -1144,13 +1144,13 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1389,7 +1389,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
@@ -1404,7 +1404,7 @@
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T4" t="n">
         <v>2.18</v>
@@ -1413,7 +1413,7 @@
         <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
         <v>2.44</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1473,7 +1473,7 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.5</v>
@@ -1482,31 +1482,31 @@
         <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="BB4" t="n">
         <v>5.3</v>
@@ -1518,13 +1518,13 @@
         <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="BF4" t="n">
         <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
         <v>1.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,7 +1643,7 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
@@ -1658,13 +1658,13 @@
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
         <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ5" t="n">
         <v>4.1</v>
       </c>
       <c r="BA5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1885,7 +1885,7 @@
         <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
@@ -1897,34 +1897,34 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="J7" t="n">
         <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
         <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
         <v>2.28</v>
@@ -2175,16 +2175,16 @@
         <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z7" t="n">
         <v>7.8</v>
@@ -2193,10 +2193,10 @@
         <v>14</v>
       </c>
       <c r="AB7" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
@@ -2205,136 +2205,136 @@
         <v>18.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH7" t="n">
         <v>38</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="AK7" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AL7" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AM7" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN7" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AO7" t="n">
         <v>10</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7" t="n">
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="BN7" t="n">
         <v>13.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BT7" t="n">
         <v>3.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2343,14 +2343,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.6</v>
+        <v>2.36</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
@@ -2925,7 +2925,7 @@
         <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.24</v>
@@ -2940,7 +2940,7 @@
         <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3173,16 +3173,16 @@
         <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
@@ -3702,7 +3702,7 @@
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,7 +3929,7 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
@@ -3956,7 +3956,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
         <v>1.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
         <v>1.15</v>
@@ -4210,7 +4210,7 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>1.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
         <v>1.23</v>
@@ -4461,7 +4461,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4933,19 +4933,19 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
         <v>1.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.35</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>2.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
         <v>3.95</v>
@@ -5226,7 +5226,7 @@
         <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5241,7 +5241,7 @@
         <v>95</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -5259,7 +5259,7 @@
         <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>75</v>
@@ -5289,10 +5289,10 @@
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5301,10 +5301,10 @@
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5316,25 +5316,25 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF19" t="n">
         <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
         <v>4.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -5462,28 +5462,28 @@
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.02</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2</v>
-      </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
         <v>970</v>
@@ -5579,7 +5579,7 @@
         <v>5.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE20" t="n">
         <v>6.6</v>
@@ -5591,68 +5591,68 @@
         <v>6.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.98</v>
+        <v>2.78</v>
       </c>
       <c r="BJ20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.72</v>
+        <v>6.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.98</v>
+        <v>14.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="BT20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
         <v>10</v>
       </c>
-      <c r="BU20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -866,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -926,7 +926,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
         <v>40</v>
@@ -947,7 +947,7 @@
         <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
@@ -956,25 +956,25 @@
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>2.62</v>
       </c>
       <c r="J3" t="n">
-        <v>1.19</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1443,10 +1443,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
@@ -1458,7 +1458,7 @@
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1467,67 +1467,67 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU4" t="n">
         <v>3.55</v>
       </c>
-      <c r="AU4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AV4" t="n">
-        <v>2.62</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE4" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
         <v>2.54</v>
@@ -1536,59 +1536,59 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="BN4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1643,22 +1643,22 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.96</v>
@@ -1667,10 +1667,10 @@
         <v>1.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1709,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3.55</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>1.14</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>1.12</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
@@ -1906,13 +1906,13 @@
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.86</v>
@@ -1933,16 +1933,16 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
@@ -1957,7 +1957,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
@@ -1975,70 +1975,70 @@
         <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
         <v>3.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
         <v>5.6</v>
@@ -2080,7 +2080,7 @@
         <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>46</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -2157,28 +2157,28 @@
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
         <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
         <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
         <v>14</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AC7" t="n">
         <v>12</v>
@@ -2202,7 +2202,7 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF7" t="n">
         <v>110</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AK7" t="n">
         <v>250</v>
@@ -2226,67 +2226,67 @@
         <v>210</v>
       </c>
       <c r="AM7" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN7" t="n">
         <v>460</v>
       </c>
       <c r="AO7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP7" t="n">
         <v>10</v>
       </c>
-      <c r="AP7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
@@ -2328,7 +2328,7 @@
         <v>3.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BV7" t="n">
         <v>9.4</v>
@@ -2346,11 +2346,11 @@
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.36</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.19</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
         <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3176,13 +3176,13 @@
         <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="R11" t="n">
         <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3953,10 +3953,10 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
         <v>1.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
         <v>1.15</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>1.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
         <v>1.23</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Q18" t="n">
         <v>1.21</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
         <v>2.24</v>
@@ -5184,13 +5184,13 @@
         <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
@@ -5202,19 +5202,19 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
         <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
         <v>1.89</v>
@@ -5223,7 +5223,7 @@
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
         <v>1.8</v>
@@ -5241,7 +5241,7 @@
         <v>95</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -5250,7 +5250,7 @@
         <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>16.5</v>
@@ -5283,16 +5283,16 @@
         <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5301,13 +5301,13 @@
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW19" t="n">
         <v>4.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
         <v>9.6</v>
@@ -5319,22 +5319,22 @@
         <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>4.9</v>
       </c>
       <c r="BD19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5</v>
       </c>
-      <c r="BE19" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF19" t="n">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5352,10 +5352,10 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO19" t="n">
         <v>4.4</v>
@@ -5379,26 +5379,26 @@
         <v>6</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
@@ -5462,7 +5462,7 @@
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
@@ -5486,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z20" t="n">
         <v>42</v>
@@ -5498,13 +5498,13 @@
         <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
         <v>13.5</v>
@@ -5513,7 +5513,7 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>70</v>
@@ -5522,10 +5522,10 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>130</v>
@@ -5537,67 +5537,67 @@
         <v>85</v>
       </c>
       <c r="AP20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>12</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AR20" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="n">
         <v>3.35</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
         <v>6.2</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5618,41 +5618,41 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
         <v>8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -872,7 +872,7 @@
         <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1138,10 +1138,10 @@
         <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
         <v>2.16</v>
@@ -1153,10 +1153,10 @@
         <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.62</v>
@@ -1219,7 +1219,7 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>3.2</v>
@@ -1240,31 +1240,31 @@
         <v>3.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>3.95</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AZ3" t="n">
         <v>3.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
         <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD3" t="n">
         <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
         <v>4.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
         <v>8.6</v>
@@ -1404,19 +1404,19 @@
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1434,7 +1434,7 @@
         <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>5.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1536,7 +1536,7 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,7 +1545,7 @@
         <v>1.13</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
         <v>3.05</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
@@ -1646,13 +1646,13 @@
         <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1730,7 +1730,7 @@
         <v>3.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AR5" t="n">
         <v>4.1</v>
@@ -1745,7 +1745,7 @@
         <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1766,19 +1766,19 @@
         <v>3.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>3.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1897,22 +1897,22 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
         <v>1.86</v>
@@ -1921,10 +1921,10 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1933,10 +1933,10 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
@@ -1948,10 +1948,10 @@
         <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1963,7 +1963,7 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
@@ -1975,7 +1975,7 @@
         <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
@@ -1984,13 +1984,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2002,61 +2002,61 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
         <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
         <v>22</v>
@@ -2068,7 +2068,7 @@
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
@@ -2077,7 +2077,7 @@
         <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
@@ -2086,17 +2086,17 @@
         <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
         <v>40</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>10.5</v>
@@ -2142,7 +2142,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -2172,7 +2172,7 @@
         <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
         <v>2.94</v>
@@ -2190,7 +2190,7 @@
         <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AB7" t="n">
         <v>29</v>
@@ -2220,7 +2220,7 @@
         <v>520</v>
       </c>
       <c r="AK7" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AL7" t="n">
         <v>210</v>
@@ -2250,7 +2250,7 @@
         <v>18.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9.199999999999999</v>
@@ -2262,16 +2262,16 @@
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>5.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
         <v>6.2</v>
@@ -2280,10 +2280,10 @@
         <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -2585,13 +2585,13 @@
         <v>4</v>
       </c>
       <c r="BV8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>6.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H11" t="n">
         <v>7.6</v>
       </c>
-      <c r="H11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>1.33</v>
+        <v>5.6</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>3.65</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>1.32</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>1.15</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>1.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>1.1</v>
@@ -4437,22 +4437,22 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,7 +4461,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -4667,230 +4667,230 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>2.76</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.21</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -5181,13 +5181,13 @@
         <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.6</v>
@@ -5211,22 +5211,22 @@
         <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
         <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5292,7 +5292,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5304,10 +5304,10 @@
         <v>4.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
         <v>9.6</v>
@@ -5316,13 +5316,13 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD19" t="n">
         <v>4.9</v>
@@ -5331,10 +5331,10 @@
         <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5388,7 +5388,7 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
@@ -5441,7 +5441,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
@@ -5453,7 +5453,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>1.34</v>
@@ -5474,7 +5474,7 @@
         <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>1.25</v>
@@ -5516,10 +5516,10 @@
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
         <v>25</v>
@@ -5555,7 +5555,7 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
         <v>4.8</v>
@@ -5573,7 +5573,7 @@
         <v>4.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -5585,7 +5585,7 @@
         <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
         <v>4.8</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -866,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -950,7 +950,7 @@
         <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
@@ -962,19 +962,19 @@
         <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1028,7 +1028,7 @@
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,7 +1046,7 @@
         <v>8.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>25</v>
@@ -1058,7 +1058,7 @@
         <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BV2" t="n">
         <v>95</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1150,13 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.62</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1398,13 @@
         <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
@@ -1545,10 +1545,10 @@
         <v>1.13</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>7.6</v>
@@ -1652,7 +1652,7 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1727,61 +1727,61 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
         <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
       </c>
       <c r="AY5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE5" t="n">
         <v>3.2</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BF5" t="n">
         <v>3.7</v>
       </c>
-      <c r="BC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BI5" t="n">
         <v>2.46</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.07</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,13 +1802,13 @@
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.86</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1906,13 +1906,13 @@
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.86</v>
@@ -1933,16 +1933,16 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>15</v>
@@ -1957,7 +1957,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
@@ -1990,19 +1990,19 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2014,25 +2014,25 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BH6" t="n">
         <v>3.15</v>
@@ -2056,7 +2056,7 @@
         <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
         <v>22</v>
@@ -2074,7 +2074,7 @@
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
         <v>1.46</v>
@@ -2178,7 +2178,7 @@
         <v>2.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>15</v>
@@ -2232,7 +2232,7 @@
         <v>460</v>
       </c>
       <c r="AO7" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>5.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
         <v>18.5</v>
@@ -2259,31 +2259,31 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>6</v>
       </c>
-      <c r="AY7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
@@ -2298,7 +2298,7 @@
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2334,7 +2334,7 @@
         <v>9.4</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
         <v>1.95</v>
@@ -2420,7 +2420,7 @@
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="T8" t="n">
         <v>1.79</v>
@@ -2477,7 +2477,7 @@
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>140</v>
@@ -2564,7 +2564,7 @@
         <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BP8" t="n">
         <v>13.5</v>
@@ -2591,7 +2591,7 @@
         <v>6.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -2635,88 +2635,88 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>19.5</v>
@@ -2725,140 +2725,140 @@
         <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP9" t="n">
         <v>20</v>
       </c>
-      <c r="AO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BQ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BN9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7</v>
-      </c>
       <c r="BU9" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>24</v>
       </c>
-      <c r="BW9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>23</v>
-      </c>
       <c r="CA9" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.9</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
         <v>19.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AZ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="BI10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -3143,73 +3143,73 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
         <v>17.5</v>
@@ -3218,155 +3218,155 @@
         <v>50</v>
       </c>
       <c r="AE11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>12</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
         <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AO11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="n">
         <v>5.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.24</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
         <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AS12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH12" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN12" t="n">
         <v>5.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -3905,94 +3905,94 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="I14" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
         <v>26</v>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
         <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>90</v>
@@ -4004,131 +4004,131 @@
         <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
         <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK14" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT14" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
+      <c r="BU14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW14" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>4.7</v>
       </c>
       <c r="BX14" t="n">
         <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ14" t="n">
         <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
         <v>34</v>
       </c>
-      <c r="Y15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
         <v>16</v>
       </c>
-      <c r="AC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>38</v>
       </c>
-      <c r="AF15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL15" t="n">
         <v>26</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="BI15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK15" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB15" t="n">
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU15" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS15" t="n">
+      <c r="BV15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA15" t="n">
         <v>6.2</v>
       </c>
-      <c r="BT15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,22 +4437,22 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,10 +4461,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.26</v>
+        <v>1.99</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -4667,55 +4667,55 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="G17" t="n">
         <v>1.68</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
         <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="S17" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="T17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="U17" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
         <v>2.46</v>
@@ -4727,13 +4727,13 @@
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -4742,7 +4742,7 @@
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
         <v>970</v>
@@ -4754,7 +4754,7 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
@@ -4772,125 +4772,125 @@
         <v>5.6</v>
       </c>
       <c r="AO17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BN17" t="n">
         <v>46</v>
       </c>
-      <c r="AP17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY17" t="n">
+      <c r="BO17" t="n">
         <v>3.3</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3</v>
-      </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.9</v>
+        <v>2.24</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>5.9</v>
+        <v>2.22</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G18" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="H18" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
         <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -4984,7 +4984,7 @@
         <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB18" t="n">
         <v>970</v>
@@ -4996,103 +4996,103 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="AW18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF18" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="n">
         <v>4.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,50 +5101,50 @@
         <v>6.2</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>5.1</v>
-      </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.6</v>
@@ -5196,16 +5196,16 @@
         <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
         <v>2.14</v>
@@ -5217,7 +5217,7 @@
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
         <v>2.06</v>
@@ -5226,7 +5226,7 @@
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5244,7 +5244,7 @@
         <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>19</v>
@@ -5256,7 +5256,7 @@
         <v>16.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
@@ -5292,7 +5292,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5304,7 +5304,7 @@
         <v>4.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5316,25 +5316,25 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5367,7 +5367,7 @@
         <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS19" t="n">
         <v>11</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
@@ -5444,7 +5444,7 @@
         <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5468,7 +5468,7 @@
         <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -5480,7 +5480,7 @@
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X20" t="n">
         <v>16</v>
@@ -5501,13 +5501,13 @@
         <v>9.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
         <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5543,13 +5543,13 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -5558,37 +5558,37 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH20" t="n">
         <v>3.35</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -875,7 +875,7 @@
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -908,7 +908,7 @@
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -950,13 +950,13 @@
         <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
         <v>7</v>
@@ -968,10 +968,10 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
         <v>10</v>
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1010,19 +1010,19 @@
         <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>8.6</v>
@@ -1052,7 +1052,7 @@
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
@@ -1064,13 +1064,13 @@
         <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
         <v>6.8</v>
@@ -1383,22 +1383,22 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1458,7 +1458,7 @@
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1467,22 +1467,22 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AT4" t="n">
         <v>5.1</v>
@@ -1491,10 +1491,10 @@
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1503,28 +1503,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1536,59 +1536,59 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
@@ -1727,16 +1727,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
         <v>3</v>
@@ -1745,43 +1745,43 @@
         <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ5" t="n">
         <v>3.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF5" t="n">
         <v>3.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI5" t="n">
         <v>2.46</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.61</v>
+        <v>9.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1915,7 +1915,7 @@
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
         <v>1.93</v>
@@ -2017,10 +2017,10 @@
         <v>6.2</v>
       </c>
       <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
         <v>40</v>
@@ -2029,7 +2029,7 @@
         <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
         <v>36</v>
@@ -2056,7 +2056,7 @@
         <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>22</v>
@@ -2074,7 +2074,7 @@
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G7" t="n">
         <v>11</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR7" t="n">
         <v>5.9</v>
@@ -2262,10 +2262,10 @@
         <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
         <v>6.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.37</v>
@@ -2405,10 +2405,10 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
@@ -2420,19 +2420,19 @@
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
         <v>17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
         <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
         <v>55</v>
@@ -2749,52 +2749,52 @@
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH9" t="n">
         <v>3.85</v>
@@ -2818,7 +2818,7 @@
         <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
         <v>20</v>
@@ -2836,7 +2836,7 @@
         <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>22</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>6.6</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.18</v>
@@ -3167,19 +3167,19 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S11" t="n">
         <v>1.9</v>
@@ -3224,7 +3224,7 @@
         <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
         <v>32</v>
@@ -3245,19 +3245,19 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO11" t="n">
         <v>140</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>36</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
         <v>11.5</v>
@@ -3299,13 +3299,13 @@
         <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI11" t="n">
         <v>4.5</v>
@@ -3323,7 +3323,7 @@
         <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
         <v>3.8</v>
@@ -3335,10 +3335,10 @@
         <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>15</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CA11" t="n">
         <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.28</v>
@@ -3430,7 +3430,7 @@
         <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.45</v>
@@ -3445,10 +3445,10 @@
         <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3475,7 +3475,7 @@
         <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
@@ -3487,19 +3487,19 @@
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
         <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>44</v>
@@ -3511,10 +3511,10 @@
         <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3526,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3538,7 +3538,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.14</v>
+        <v>3.9</v>
       </c>
       <c r="BB12" t="n">
         <v>18</v>
@@ -3547,16 +3547,16 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
         <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -3660,7 +3660,7 @@
         <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3672,7 +3672,7 @@
         <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>5.8</v>
@@ -3699,7 +3699,7 @@
         <v>2.54</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
         <v>2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W14" t="n">
         <v>1.3</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4195,7 +4195,7 @@
         <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
         <v>2.34</v>
@@ -4210,7 +4210,7 @@
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="H16" t="n">
         <v>1.56</v>
@@ -4428,10 +4428,10 @@
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
@@ -4440,7 +4440,7 @@
         <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
         <v>1.87</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>5.2</v>
+        <v>2.76</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>2.52</v>
       </c>
       <c r="G18" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H18" t="n">
         <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -4957,10 +4957,10 @@
         <v>1.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
         <v>1.58</v>
@@ -4972,7 +4972,7 @@
         <v>1.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -4999,10 +4999,10 @@
         <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>970</v>
@@ -5026,10 +5026,10 @@
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ18" t="n">
         <v>10.5</v>
@@ -5038,49 +5038,49 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT18" t="n">
         <v>4.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AZ18" t="n">
         <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC18" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH18" t="n">
         <v>4.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -863,16 +863,16 @@
         <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,28 +881,28 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -923,13 +923,13 @@
         <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AE2" t="n">
         <v>180</v>
@@ -941,10 +941,10 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>150</v>
+        <v>470</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -953,13 +953,13 @@
         <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO2" t="n">
         <v>250</v>
@@ -968,13 +968,13 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1007,16 +1007,16 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1025,7 +1025,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
         <v>9.199999999999999</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
@@ -1052,7 +1052,7 @@
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
@@ -1064,13 +1064,13 @@
         <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1165,112 +1165,112 @@
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
         <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
         <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>3.8</v>
@@ -1392,13 +1392,13 @@
         <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
         <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
@@ -1416,31 +1416,31 @@
         <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
         <v>9.6</v>
@@ -1452,37 +1452,37 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>5.1</v>
@@ -1494,7 +1494,7 @@
         <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1503,28 +1503,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1548,7 +1548,7 @@
         <v>3.95</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
         <v>7.6</v>
@@ -1652,7 +1652,7 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1673,16 +1673,16 @@
         <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>8.6</v>
@@ -1694,91 +1694,91 @@
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
         <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
         <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
         <v>5.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
         <v>2.74</v>
@@ -1882,7 +1882,7 @@
         <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1921,22 +1921,22 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
         <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
@@ -1951,7 +1951,7 @@
         <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1972,7 +1972,7 @@
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>32</v>
@@ -1981,7 +1981,7 @@
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.4</v>
@@ -1990,7 +1990,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2014,25 +2014,25 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>40</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
         <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="n">
         <v>3.15</v>
@@ -2074,7 +2074,7 @@
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
         <v>6.8</v>
@@ -2196,10 +2196,10 @@
         <v>29</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -2208,13 +2208,13 @@
         <v>110</v>
       </c>
       <c r="AG7" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AH7" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="n">
         <v>520</v>
@@ -2259,31 +2259,31 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
@@ -2298,7 +2298,7 @@
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -2405,7 +2405,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -2420,7 +2420,7 @@
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.8</v>
@@ -2432,10 +2432,10 @@
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
         <v>19.5</v>
@@ -2444,7 +2444,7 @@
         <v>48</v>
       </c>
       <c r="AA8" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>9.4</v>
@@ -2456,7 +2456,7 @@
         <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2468,7 +2468,7 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -2480,67 +2480,67 @@
         <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX8" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4</v>
-      </c>
       <c r="AY8" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA8" t="n">
         <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
         <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H9" t="n">
         <v>2.66</v>
@@ -2668,13 +2668,13 @@
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
         <v>1.64</v>
@@ -2683,7 +2683,7 @@
         <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
         <v>1.54</v>
@@ -2692,22 +2692,22 @@
         <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
         <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
@@ -2716,10 +2716,10 @@
         <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>48</v>
@@ -2734,73 +2734,73 @@
         <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO9" t="n">
         <v>25</v>
       </c>
-      <c r="AO9" t="n">
-        <v>28</v>
-      </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
         <v>11</v>
       </c>
       <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
       <c r="BD9" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
         <v>1.89</v>
@@ -2898,169 +2898,169 @@
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
         <v>2.12</v>
       </c>
       <c r="X10" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="Y10" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9</v>
       </c>
-      <c r="AO10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>5.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
         <v>12</v>
@@ -3084,7 +3084,7 @@
         <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT10" t="n">
         <v>8.800000000000001</v>
@@ -3096,23 +3096,23 @@
         <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
         <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -3143,94 +3143,94 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>320</v>
       </c>
       <c r="Z11" t="n">
         <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AD11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AE11" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="AJ11" t="n">
         <v>11.5</v>
@@ -3242,25 +3242,25 @@
         <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AO11" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
         <v>36</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -3272,7 +3272,7 @@
         <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3284,7 +3284,7 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
@@ -3296,22 +3296,22 @@
         <v>24</v>
       </c>
       <c r="BE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BG11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>11</v>
-      </c>
       <c r="BH11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>9</v>
@@ -3323,25 +3323,25 @@
         <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO11" t="n">
         <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BR11" t="n">
         <v>18</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BU11" t="n">
         <v>11</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CA11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
         <v>4.1</v>
@@ -3412,16 +3412,16 @@
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3433,7 +3433,7 @@
         <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
         <v>2.78</v>
@@ -3448,22 +3448,22 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>10.5</v>
@@ -3472,13 +3472,13 @@
         <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>19.5</v>
@@ -3490,31 +3490,31 @@
         <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP12" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3526,19 +3526,19 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.9</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
         <v>18</v>
@@ -3547,16 +3547,16 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
         <v>3.55</v>
@@ -3702,22 +3702,22 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
         <v>13</v>
@@ -3726,49 +3726,49 @@
         <v>19.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
         <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AN13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3777,40 +3777,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
         <v>4.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -3905,118 +3905,118 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G14" t="n">
         <v>3.6</v>
       </c>
-      <c r="G14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="H14" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R14" t="n">
         <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
         <v>26</v>
       </c>
-      <c r="AB14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>22</v>
-      </c>
       <c r="AF14" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH14" t="n">
         <v>17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AK14" t="n">
         <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
         <v>11.5</v>
@@ -4025,7 +4025,7 @@
         <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7.4</v>
@@ -4034,101 +4034,101 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
       </c>
       <c r="BA14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ14" t="n">
         <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
         <v>3.05</v>
@@ -4213,7 +4213,7 @@
         <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4267,7 +4267,7 @@
         <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>16</v>
@@ -4303,7 +4303,7 @@
         <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC15" t="n">
         <v>17</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
         <v>1.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.28</v>
@@ -4440,7 +4440,7 @@
         <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
         <v>1.87</v>
@@ -4449,130 +4449,130 @@
         <v>1.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
         <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="G17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
         <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="S17" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="T17" t="n">
         <v>1.51</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4727,130 +4727,130 @@
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="AA17" t="n">
         <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AF17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH17" t="n">
         <v>970</v>
       </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>950</v>
-      </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AO17" t="n">
         <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW17" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BN17" t="n">
-        <v>46</v>
+        <v>5.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
@@ -4862,35 +4862,35 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
         <v>4.7</v>
       </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G18" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.29</v>
@@ -4945,148 +4945,148 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
         <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
         <v>1.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH18" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BI18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5104,19 +5104,19 @@
         <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
@@ -5128,7 +5128,7 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
         <v>3.3</v>
@@ -5205,10 +5205,10 @@
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
         <v>1.3</v>
@@ -5217,16 +5217,16 @@
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5244,7 +5244,7 @@
         <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>19</v>
@@ -5253,7 +5253,7 @@
         <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -5265,10 +5265,10 @@
         <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -5277,7 +5277,7 @@
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>70</v>
@@ -5292,7 +5292,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5301,10 +5301,10 @@
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5316,7 +5316,7 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB19" t="n">
         <v>4.8</v>
@@ -5325,16 +5325,16 @@
         <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
         <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
         <v>3.15</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.9</v>
@@ -5361,16 +5361,16 @@
         <v>4.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ19" t="n">
         <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5382,13 +5382,13 @@
         <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
@@ -5441,10 +5441,10 @@
         <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5468,7 +5468,7 @@
         <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -5480,7 +5480,7 @@
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X20" t="n">
         <v>16</v>
@@ -5507,7 +5507,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5543,13 +5543,13 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -5558,37 +5558,37 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.35</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H2" t="n">
         <v>9.4</v>
@@ -872,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
@@ -896,13 +896,13 @@
         <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -929,13 +929,13 @@
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE2" t="n">
         <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -959,34 +959,34 @@
         <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO2" t="n">
         <v>250</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,28 +995,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
         <v>3.85</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1392,25 +1392,25 @@
         <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
         <v>1.14</v>
@@ -1419,7 +1419,7 @@
         <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1446,7 +1446,7 @@
         <v>9.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
@@ -1455,7 +1455,7 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AK4" t="n">
         <v>500</v>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>5.1</v>
@@ -1494,7 +1494,7 @@
         <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1503,28 +1503,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
         <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
         <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1646,13 +1646,13 @@
         <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1670,7 +1670,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
@@ -1733,10 +1733,10 @@
         <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
         <v>3.85</v>
@@ -1745,10 +1745,10 @@
         <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
@@ -1760,28 +1760,28 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="BF5" t="n">
         <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BI5" t="n">
         <v>2.46</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.4</v>
+        <v>1.61</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
         <v>2.74</v>
@@ -1882,7 +1882,7 @@
         <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1915,10 +1915,10 @@
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
         <v>1.43</v>
@@ -1939,7 +1939,7 @@
         <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
@@ -1990,7 +1990,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2014,22 +2014,22 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
         <v>8</v>
@@ -2056,7 +2056,7 @@
         <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
         <v>22</v>
@@ -2074,7 +2074,7 @@
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
         <v>1.65</v>
@@ -2190,13 +2190,13 @@
         <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
         <v>29</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>11</v>
@@ -2214,7 +2214,7 @@
         <v>70</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>520</v>
@@ -2253,13 +2253,13 @@
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
         <v>16</v>
@@ -2268,22 +2268,22 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
@@ -2298,7 +2298,7 @@
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2334,7 +2334,7 @@
         <v>9.4</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
         <v>4.7</v>
@@ -2429,7 +2429,7 @@
         <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>2.08</v>
@@ -2507,7 +2507,7 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW8" t="n">
         <v>5.7</v>
@@ -2519,16 +2519,16 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
         <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
         <v>5.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
         <v>1.54</v>
@@ -2752,7 +2752,7 @@
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
         <v>7.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>12.5</v>
       </c>
       <c r="I11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>7.4</v>
@@ -3188,7 +3188,7 @@
         <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>1.07</v>
@@ -3206,7 +3206,7 @@
         <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
         <v>16.5</v>
@@ -3227,7 +3227,7 @@
         <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
         <v>510</v>
@@ -3248,7 +3248,7 @@
         <v>3.05</v>
       </c>
       <c r="AO11" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
@@ -3272,7 +3272,7 @@
         <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3299,7 +3299,7 @@
         <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
@@ -3362,11 +3362,11 @@
         <v>7</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
         <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -3421,7 +3421,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3448,7 +3448,7 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3514,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3550,7 +3550,7 @@
         <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>3.55</v>
@@ -3702,7 +3702,7 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -3777,7 +3777,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW13" t="n">
         <v>6</v>
@@ -3798,7 +3798,7 @@
         <v>5.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
         <v>5.7</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3947,7 +3947,7 @@
         <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
         <v>2.26</v>
@@ -4058,7 +4058,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
         <v>28</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
         <v>1.59</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -4775,19 +4775,19 @@
         <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
         <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AU17" t="n">
         <v>5.9</v>
@@ -4796,31 +4796,31 @@
         <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>3.45</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
         <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
         <v>6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
         <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I19" t="n">
         <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
         <v>3.3</v>
@@ -5205,7 +5205,7 @@
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
         <v>2.12</v>
@@ -5223,10 +5223,10 @@
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -5304,7 +5304,7 @@
         <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5319,13 +5319,13 @@
         <v>5.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE19" t="n">
         <v>5.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
@@ -5441,7 +5441,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
@@ -5462,7 +5462,7 @@
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
@@ -5471,16 +5471,16 @@
         <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X20" t="n">
         <v>16</v>
@@ -5543,13 +5543,13 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -5558,37 +5558,37 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BA20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB20" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>3.35</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
         <v>1.44</v>
@@ -884,7 +884,7 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.18</v>
@@ -902,7 +902,7 @@
         <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -917,7 +917,7 @@
         <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>100</v>
+        <v>530</v>
       </c>
       <c r="AA2" t="n">
         <v>390</v>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AE2" t="n">
         <v>180</v>
@@ -953,7 +953,7 @@
         <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>390</v>
@@ -968,13 +968,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
         <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,7 +995,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
         <v>42</v>
@@ -1007,22 +1007,22 @@
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.85</v>
@@ -1043,7 +1043,7 @@
         <v>3.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.8</v>
@@ -1052,7 +1052,7 @@
         <v>25</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT2" t="n">
         <v>12.5</v>
@@ -1064,13 +1064,13 @@
         <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1135,43 +1135,43 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
         <v>75</v>
@@ -1180,13 +1180,13 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>29</v>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>120</v>
@@ -1204,7 +1204,7 @@
         <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AL3" t="n">
         <v>160</v>
@@ -1213,128 +1213,128 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR3" t="n">
         <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
         <v>5.9</v>
       </c>
-      <c r="BH3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.36</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.22</v>
+        <v>9.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -1380,7 +1380,7 @@
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1395,7 +1395,7 @@
         <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
         <v>2.24</v>
@@ -1407,10 +1407,10 @@
         <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
         <v>1.14</v>
@@ -1422,7 +1422,7 @@
         <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1437,13 +1437,13 @@
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>21</v>
@@ -1473,28 +1473,28 @@
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
         <v>5.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1503,28 +1503,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
@@ -1536,16 +1536,16 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO4" t="n">
         <v>3.15</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
         <v>6</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1622,37 +1622,37 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1661,7 +1661,7 @@
         <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
         <v>1.82</v>
@@ -1670,7 +1670,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1700,7 +1700,7 @@
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
         <v>500</v>
@@ -1709,7 +1709,7 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
@@ -1730,25 +1730,25 @@
         <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
@@ -1757,34 +1757,34 @@
         <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>2.74</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
         <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.74</v>
@@ -1885,10 +1885,10 @@
         <v>3.45</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1912,10 +1912,10 @@
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
         <v>1.92</v>
@@ -1933,10 +1933,10 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>9.6</v>
@@ -1951,7 +1951,7 @@
         <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1990,7 +1990,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2011,10 +2011,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>7.2</v>
@@ -2023,16 +2023,16 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>6.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BH6" t="n">
         <v>3.15</v>
@@ -2044,7 +2044,7 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2074,7 +2074,7 @@
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.46</v>
@@ -2157,7 +2157,7 @@
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
         <v>2.06</v>
@@ -2166,19 +2166,19 @@
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -2205,31 +2205,31 @@
         <v>19</v>
       </c>
       <c r="AF7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG7" t="n">
         <v>85</v>
       </c>
       <c r="AH7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="AK7" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AL7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="AO7" t="n">
         <v>9.6</v>
@@ -2241,49 +2241,49 @@
         <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
         <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
         <v>8</v>
@@ -2298,59 +2298,59 @@
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.64</v>
+        <v>12</v>
       </c>
       <c r="BN7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BU7" t="n">
         <v>3.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H8" t="n">
         <v>4.7</v>
@@ -2393,7 +2393,7 @@
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -2405,7 +2405,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -2432,7 +2432,7 @@
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
         <v>16.5</v>
@@ -2495,7 +2495,7 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
         <v>5.9</v>
@@ -2519,10 +2519,10 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
         <v>9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
         <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>1.89</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G11" t="n">
         <v>1.27</v>
@@ -3152,7 +3152,7 @@
         <v>12.5</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
         <v>7.4</v>
@@ -3188,7 +3188,7 @@
         <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.07</v>
@@ -3203,7 +3203,7 @@
         <v>320</v>
       </c>
       <c r="Z11" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA11" t="n">
         <v>500</v>
@@ -3215,7 +3215,7 @@
         <v>23</v>
       </c>
       <c r="AD11" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>200</v>
@@ -3227,7 +3227,7 @@
         <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>510</v>
@@ -3242,7 +3242,7 @@
         <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
         <v>3.05</v>
@@ -3272,7 +3272,7 @@
         <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3314,7 +3314,7 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3335,16 +3335,16 @@
         <v>5.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="BS11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>16.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>7</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
@@ -3409,7 +3409,7 @@
         <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -3550,7 +3550,7 @@
         <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -3681,16 +3681,16 @@
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
         <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.51</v>
@@ -3702,13 +3702,13 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z13" t="n">
         <v>80</v>
@@ -3720,10 +3720,10 @@
         <v>16</v>
       </c>
       <c r="AC13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
@@ -3744,7 +3744,7 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -3756,19 +3756,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3777,46 +3777,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY13" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
         <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
         <v>9</v>
@@ -3834,13 +3834,13 @@
         <v>5.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
@@ -3849,13 +3849,13 @@
         <v>6.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU13" t="n">
         <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
         <v>7.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
         <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="n">
         <v>2.42</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
         <v>3.05</v>
@@ -4210,7 +4210,7 @@
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>4.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>8.800000000000001</v>
@@ -4342,7 +4342,7 @@
         <v>5.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
         <v>15.5</v>
@@ -4360,7 +4360,7 @@
         <v>7.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>23</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4419,34 +4419,34 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -4461,7 +4461,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>1.67</v>
@@ -5053,7 +5053,7 @@
         <v>6.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY18" t="n">
         <v>7</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="BN18" t="n">
         <v>6.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -5181,13 +5181,13 @@
         <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
         <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.5</v>
@@ -5214,7 +5214,7 @@
         <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
         <v>1.87</v>
@@ -5304,7 +5304,7 @@
         <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5322,10 +5322,10 @@
         <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
         <v>5.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
@@ -5453,7 +5453,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.34</v>
@@ -5480,7 +5480,7 @@
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X20" t="n">
         <v>16</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
         <v>6.6</v>
@@ -5564,7 +5564,7 @@
         <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="AZ20" t="n">
         <v>5.3</v>
@@ -5579,7 +5579,7 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
         <v>6.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,94 +881,94 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="Z2" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="AA2" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="n">
         <v>470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>40</v>
@@ -980,97 +980,97 @@
         <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
         <v>48</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>17.5</v>
+        <v>130</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1111,103 +1111,103 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
         <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
         <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
         <v>75</v>
       </c>
-      <c r="AB3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
       <c r="AF3" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
         <v>370</v>
       </c>
       <c r="AL3" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1216,125 +1216,125 @@
         <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
         <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>1.86</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>1.88</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>1.89</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1368,61 +1368,61 @@
         <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
         <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1431,22 +1431,22 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
@@ -1467,128 +1467,128 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
         <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1697,10 +1697,10 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>500</v>
@@ -1730,119 +1730,119 @@
         <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
         <v>4.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>2.06</v>
       </c>
       <c r="BF5" t="n">
         <v>3.8</v>
       </c>
       <c r="BG5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>2.4</v>
       </c>
-      <c r="BH5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>5.6</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.13</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
         <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>1.92</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>1.99</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>2.64</v>
       </c>
       <c r="BD6" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>1.93</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>3.05</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>2.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="V7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
         <v>29</v>
       </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>480</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>420</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>3.05</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>2.24</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>2.16</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>2.82</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2381,109 +2381,109 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="G8" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
@@ -2492,13 +2492,13 @@
         <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>2.78</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.9</v>
+        <v>2.52</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
@@ -2507,10 +2507,10 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>2.32</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>2.52</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
@@ -2519,92 +2519,92 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>2.72</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X9" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW9" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>1.97</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>1.93</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>1.99</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>2.04</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>2.02</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>2.04</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
         <v>140</v>
@@ -2955,164 +2955,164 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
         <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>21</v>
+        <v>1.95</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>1.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>1.72</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>1.74</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>1.81</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>1.72</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>1.73</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>1.82</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>1.76</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>1.92</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>1.72</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>2.02</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>1.94</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>1.92</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>1.96</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>1.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
         <v>950</v>
       </c>
-      <c r="Y11" t="n">
-        <v>320</v>
-      </c>
       <c r="Z11" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
         <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>510</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.5</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.05</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>1.45</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>1.54</v>
       </c>
       <c r="AV11" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>1.41</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>1.54</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>1.42</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>1.44</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>1.54</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
         <v>4.7</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.8</v>
+        <v>2.52</v>
       </c>
       <c r="BP11" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="BR11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BT11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X12" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT12" t="n">
         <v>1.92</v>
       </c>
-      <c r="X12" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>30</v>
+        <v>1.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>1.98</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>1.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>18</v>
+        <v>2.08</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>1.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="BG12" t="n">
         <v>5.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>4.9</v>
       </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="Q13" t="n">
         <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="U13" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
         <v>85</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AO13" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>1.95</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>1.91</v>
       </c>
       <c r="AR13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH13" t="n">
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BI13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN13" t="n">
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>5.4</v>
       </c>
-      <c r="BO13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BZ13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>13</v>
+        <v>2.04</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>2.08</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>1.98</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>2.08</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>1.97</v>
       </c>
       <c r="BA14" t="n">
-        <v>16</v>
+        <v>2.08</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>2.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>2.08</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>2.12</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
         <v>3.05</v>
@@ -4171,40 +4171,40 @@
         <v>3.45</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>1.41</v>
@@ -4213,176 +4213,176 @@
         <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="n">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>1.84</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>1.83</v>
       </c>
       <c r="AS15" t="n">
-        <v>30</v>
+        <v>1.84</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>12.5</v>
+        <v>1.81</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>1.84</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.76</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>1.83</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>1.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>1.83</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>34</v>
+        <v>1.85</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>4.6</v>
       </c>
-      <c r="BI15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BR15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BX15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4413,58 +4413,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="I16" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
         <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4503,7 +4503,7 @@
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>500</v>
@@ -4515,64 +4515,64 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BF16" t="n">
         <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.2</v>
@@ -4691,34 +4691,34 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4730,13 +4730,13 @@
         <v>350</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4745,10 +4745,10 @@
         <v>320</v>
       </c>
       <c r="AF17" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
@@ -4769,128 +4769,128 @@
         <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
         <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.3</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.9</v>
+        <v>1.74</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.3</v>
+        <v>1.72</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>1.79</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.8</v>
+        <v>1.79</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>1.85</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4921,64 +4921,64 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
         <v>1.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -4987,10 +4987,10 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -5005,7 +5005,7 @@
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
@@ -5023,128 +5023,128 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>2.02</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>1.96</v>
       </c>
       <c r="AU18" t="n">
         <v>5.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>1.92</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>2.06</v>
       </c>
       <c r="AX18" t="n">
-        <v>6</v>
+        <v>2.06</v>
       </c>
       <c r="AY18" t="n">
-        <v>7</v>
+        <v>1.92</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>1.98</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>2.08</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.4</v>
+        <v>2.06</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>2.08</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="BF18" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
         <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>1.19</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>1.19</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>1.19</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.78</v>
       </c>
       <c r="AV19" t="n">
-        <v>14</v>
+        <v>1.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>1.19</v>
       </c>
       <c r="AX19" t="n">
-        <v>11.5</v>
+        <v>1.19</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>1.19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>1.19</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>1.19</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>1.12</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.4</v>
+        <v>1.19</v>
       </c>
       <c r="BF19" t="n">
-        <v>15</v>
+        <v>1.07</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -5456,203 +5456,203 @@
         <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>9.800000000000001</v>
@@ -875,46 +875,46 @@
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
         <v>540</v>
@@ -923,100 +923,100 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AD2" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>470</v>
+        <v>260</v>
       </c>
       <c r="AJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="AK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AW2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
         <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>22</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>18.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
@@ -1141,7 +1141,7 @@
         <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
         <v>2.28</v>
@@ -1156,13 +1156,13 @@
         <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1189,7 +1189,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1198,22 +1198,22 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
@@ -1237,10 +1237,10 @@
         <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.86</v>
+        <v>11.5</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,22 +1252,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BB3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.89</v>
       </c>
-      <c r="BC3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
         <v>1.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.89</v>
       </c>
       <c r="BG3" t="n">
         <v>5.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.49</v>
@@ -1389,22 +1389,22 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.8</v>
@@ -1413,10 +1413,10 @@
         <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1470,7 +1470,7 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>5.5</v>
@@ -1518,7 +1518,7 @@
         <v>2.56</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BF4" t="n">
         <v>3.45</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
         <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.44</v>
@@ -1661,19 +1661,19 @@
         <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1724,7 +1724,7 @@
         <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>5.6</v>
@@ -1733,10 +1733,10 @@
         <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AT5" t="n">
         <v>3.85</v>
@@ -1748,7 +1748,7 @@
         <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
         <v>4.9</v>
@@ -1760,7 +1760,7 @@
         <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BB5" t="n">
         <v>7.8</v>
@@ -1769,16 +1769,16 @@
         <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BF5" t="n">
         <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1897,37 +1897,37 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
         <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AT6" t="n">
         <v>5.1</v>
@@ -2002,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AX6" t="n">
         <v>6.6</v>
@@ -2014,28 +2014,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
         <v>1.04</v>
@@ -2044,31 +2044,31 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I7" t="n">
         <v>1.53</v>
@@ -2148,7 +2148,7 @@
         <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>3.4</v>
@@ -2157,16 +2157,16 @@
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
         <v>2.02</v>
@@ -2181,7 +2181,7 @@
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2196,7 +2196,7 @@
         <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2265,10 +2265,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="BB7" t="n">
         <v>4.2</v>
@@ -2280,7 +2280,7 @@
         <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
@@ -2289,7 +2289,7 @@
         <v>2.82</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
         <v>1.04</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
         <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2465,7 +2465,7 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>320</v>
@@ -2486,19 +2486,19 @@
         <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
@@ -2507,10 +2507,10 @@
         <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
@@ -2519,19 +2519,19 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="BE8" t="n">
         <v>2.5</v>
@@ -2540,7 +2540,7 @@
         <v>3.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2638,25 +2638,25 @@
         <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H9" t="n">
         <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
         <v>4.1</v>
@@ -2686,7 +2686,7 @@
         <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
@@ -2743,49 +2743,49 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.94</v>
+        <v>2.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.88</v>
+        <v>2.74</v>
       </c>
       <c r="AU9" t="n">
         <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.97</v>
+        <v>2.76</v>
       </c>
       <c r="AY9" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="BE9" t="n">
         <v>2.06</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
@@ -2916,19 +2916,19 @@
         <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
         <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.65</v>
@@ -2937,10 +2937,10 @@
         <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2994,62 +2994,62 @@
         <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AX10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG10" t="n">
         <v>1.82</v>
       </c>
-      <c r="AY10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>1.21</v>
@@ -3179,22 +3179,22 @@
         <v>1.37</v>
       </c>
       <c r="R11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S11" t="n">
         <v>1.94</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3403,46 +3403,46 @@
         <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
         <v>1.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3457,7 +3457,7 @@
         <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
@@ -3472,7 +3472,7 @@
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
         <v>970</v>
@@ -3484,16 +3484,16 @@
         <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3505,58 +3505,58 @@
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="AU12" t="n">
         <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AY12" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.98</v>
+        <v>1.49</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
         <v>2.18</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.8</v>
+        <v>1.57</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -3675,34 +3675,34 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
         <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="U13" t="n">
         <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3759,58 +3759,58 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AU13" t="n">
         <v>5.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF13" t="n">
         <v>2.02</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
         <v>3.45</v>
@@ -3914,13 +3914,13 @@
         <v>2.24</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -3941,19 +3941,19 @@
         <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="V14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
         <v>1.41</v>
@@ -4010,10 +4010,10 @@
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
         <v>6.2</v>
@@ -4022,10 +4022,10 @@
         <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AU14" t="n">
         <v>5.6</v>
@@ -4034,31 +4034,31 @@
         <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BF14" t="n">
         <v>5.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.28</v>
@@ -4189,28 +4189,28 @@
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
         <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4249,7 +4249,7 @@
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -4267,52 +4267,52 @@
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.83</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.84</v>
+        <v>5.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.83</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
         <v>1.84</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
         <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.81</v>
+        <v>4.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.84</v>
+        <v>4.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.83</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="BF15" t="n">
         <v>4.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4419,40 +4419,40 @@
         <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="I16" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
         <v>4.3</v>
       </c>
-      <c r="K16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.78</v>
@@ -4461,7 +4461,7 @@
         <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
@@ -4515,7 +4515,7 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -4524,10 +4524,10 @@
         <v>1.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AS16" t="n">
         <v>1.28</v>
@@ -4536,7 +4536,7 @@
         <v>1.28</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AV16" t="n">
         <v>1.25</v>
@@ -4545,7 +4545,7 @@
         <v>1.27</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AY16" t="n">
         <v>1.28</v>
@@ -4554,7 +4554,7 @@
         <v>1.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BB16" t="n">
         <v>1.29</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -4697,16 +4697,16 @@
         <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
         <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
         <v>1.27</v>
@@ -4715,10 +4715,10 @@
         <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4775,7 +4775,7 @@
         <v>38</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ17" t="n">
         <v>4.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4921,46 +4921,46 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I18" t="n">
         <v>2.58</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.76</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
         <v>1.32</v>
@@ -4969,10 +4969,10 @@
         <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -5023,7 +5023,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
         <v>500</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
         <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
@@ -5190,16 +5190,16 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.39</v>
@@ -5229,10 +5229,10 @@
         <v>1.8</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -5241,19 +5241,19 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
@@ -5265,10 +5265,10 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -5277,64 +5277,64 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.78</v>
+        <v>1.09</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.94</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.99</v>
       </c>
       <c r="H20" t="n">
         <v>4.4</v>
@@ -5441,10 +5441,10 @@
         <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -5453,16 +5453,16 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
@@ -5480,7 +5480,7 @@
         <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -863,46 +863,46 @@
         <v>1.42</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K2" t="n">
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
@@ -914,163 +914,163 @@
         <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>540</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO2" t="n">
         <v>170</v>
       </c>
-      <c r="AN2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>180</v>
-      </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AS2" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
         <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="n">
         <v>130</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT2" t="n">
         <v>12</v>
       </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BP3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.49</v>
@@ -1389,37 +1389,37 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,10 +1431,10 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1443,10 +1443,10 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
@@ -1455,13 +1455,13 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="n">
         <v>700</v>
@@ -1470,125 +1470,125 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1643,34 +1643,34 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
         <v>13.5</v>
@@ -1685,10 +1685,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1697,13 +1697,13 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1712,7 +1712,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1730,16 +1730,16 @@
         <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.16</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.04</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
         <v>4.9</v>
@@ -1748,19 +1748,19 @@
         <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.12</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
         <v>7.8</v>
@@ -1769,80 +1769,80 @@
         <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>2.12</v>
       </c>
-      <c r="BF5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1900,203 +1900,203 @@
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>370</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>290</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>9</v>
       </c>
-      <c r="AS6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.38</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.38</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.38</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.49</v>
@@ -2142,19 +2142,19 @@
         <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
         <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.82</v>
@@ -2169,188 +2169,188 @@
         <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AI7" t="n">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
         <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.95</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.02</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.61</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
         <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
         <v>42</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU8" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.37</v>
@@ -2659,7 +2659,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.27</v>
@@ -2677,58 +2677,58 @@
         <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
         <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
         <v>95</v>
@@ -2737,128 +2737,128 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>26</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.72</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.2</v>
+        <v>16.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.74</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.34</v>
+        <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.76</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
@@ -2913,40 +2913,40 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
         <v>2.12</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
         <v>140</v>
@@ -2955,164 +2955,164 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
         <v>19</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>85</v>
+        <v>8.4</v>
       </c>
       <c r="AO10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX10" t="n">
         <v>36</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>1.29</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.21</v>
@@ -3170,7 +3170,7 @@
         <v>7.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P11" t="n">
         <v>3.35</v>
@@ -3179,194 +3179,194 @@
         <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.13</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.12</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
         <v>510</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>3.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.45</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.54</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.43</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.41</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.54</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.42</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.5</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.54</v>
+        <v>20</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -3418,31 +3418,31 @@
         <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3451,176 +3451,176 @@
         <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX12" t="n">
         <v>42</v>
       </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY12" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -3678,67 +3678,67 @@
         <v>6.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q13" t="n">
         <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
@@ -3747,7 +3747,7 @@
         <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
@@ -3756,125 +3756,125 @@
         <v>85</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.04</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.94</v>
+        <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.99</v>
+        <v>5.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.94</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.95</v>
+        <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.46</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.92</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.95</v>
+        <v>18.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.89</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.97</v>
+        <v>15</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU13" t="n">
         <v>4.2</v>
       </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -3947,188 +3947,188 @@
         <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
         <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE14" t="n">
         <v>42</v>
       </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>500</v>
-      </c>
       <c r="AF14" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.08</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>7</v>
       </c>
-      <c r="AS14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="n">
         <v>3.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.28</v>
@@ -4183,13 +4183,13 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
         <v>1.54</v>
@@ -4201,188 +4201,188 @@
         <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="V15" t="n">
         <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X15" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>600</v>
+        <v>23</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN15" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BO15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS15" t="n">
         <v>7</v>
       </c>
-      <c r="BE15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I16" t="n">
         <v>1.77</v>
@@ -4428,79 +4428,79 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.79</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.78</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA16" t="n">
         <v>500</v>
       </c>
-      <c r="AA16" t="n">
-        <v>900</v>
-      </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AC16" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
       </c>
       <c r="AF16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AG16" t="n">
         <v>500</v>
       </c>
-      <c r="AG16" t="n">
-        <v>950</v>
-      </c>
       <c r="AH16" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
@@ -4515,128 +4515,128 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.23</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.28</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.28</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.27</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.28</v>
+        <v>18.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.28</v>
+        <v>16.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.27</v>
+        <v>8.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.28</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>5.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.29</v>
+        <v>9.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.21</v>
@@ -4691,7 +4691,7 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
@@ -4703,22 +4703,22 @@
         <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4730,10 +4730,10 @@
         <v>350</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -4748,7 +4748,7 @@
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
@@ -4757,7 +4757,7 @@
         <v>150</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
         <v>970</v>
@@ -4769,128 +4769,128 @@
         <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.89</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
         <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.72</v>
+        <v>5.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.79</v>
+        <v>6.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.79</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
         <v>3.15</v>
@@ -4936,7 +4936,7 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -4951,10 +4951,10 @@
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R18" t="n">
         <v>1.51</v>
@@ -4963,37 +4963,37 @@
         <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
         <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z18" t="n">
         <v>970</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>500</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE18" t="n">
         <v>500</v>
@@ -5002,10 +5002,10 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
@@ -5023,128 +5023,128 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.94</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.96</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO18" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
@@ -5208,7 +5208,7 @@
         <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
@@ -5217,188 +5217,188 @@
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.09</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.09</v>
+        <v>34</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.09</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.09</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>16</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>16</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -5429,28 +5429,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G20" t="n">
         <v>1.94</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
         <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
         <v>3.7</v>
@@ -5471,10 +5471,10 @@
         <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>1.27</v>
@@ -5483,176 +5483,176 @@
         <v>2.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>11</v>
       </c>
-      <c r="AV2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>1.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>90</v>
+        <v>1.2</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>1.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>1.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>1.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BG2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -1129,10 +1129,10 @@
         <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
@@ -1153,28 +1153,28 @@
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
         <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
@@ -1204,7 +1204,7 @@
         <v>250</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="AL3" t="n">
         <v>160</v>
@@ -1219,13 +1219,13 @@
         <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
         <v>10.5</v>
@@ -1264,77 +1264,77 @@
         <v>15</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BN3" t="n">
         <v>6.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT3" t="n">
         <v>5.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I4" t="n">
         <v>7.4</v>
       </c>
-      <c r="I4" t="n">
-        <v>8.6</v>
-      </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1386,40 +1386,40 @@
         <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
         <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,106 +1431,106 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM4" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
         <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
         <v>12.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
         <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,31 +1542,31 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU4" t="n">
         <v>6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1619,88 +1619,88 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1709,10 +1709,10 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,128 +1721,128 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>2.08</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>2.32</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>1.96</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
@@ -1897,49 +1897,49 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
@@ -1951,7 +1951,7 @@
         <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1981,7 +1981,7 @@
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1990,7 +1990,7 @@
         <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
         <v>7.4</v>
@@ -2002,37 +2002,37 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BN6" t="n">
         <v>5.3</v>
@@ -2074,7 +2074,7 @@
         <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
         <v>34</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="n">
         <v>1.53</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -2169,22 +2169,22 @@
         <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
         <v>8</v>
@@ -2193,7 +2193,7 @@
         <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
@@ -2202,34 +2202,34 @@
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AF7" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AG7" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AH7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="n">
         <v>460</v>
       </c>
       <c r="AK7" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AL7" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AM7" t="n">
-        <v>270</v>
+        <v>790</v>
       </c>
       <c r="AN7" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AO7" t="n">
         <v>9.800000000000001</v>
@@ -2238,7 +2238,7 @@
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>6.8</v>
@@ -2250,107 +2250,107 @@
         <v>20</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
         <v>13</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BN7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G8" t="n">
         <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.4</v>
@@ -2420,16 +2420,16 @@
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>2.24</v>
@@ -2438,7 +2438,7 @@
         <v>16.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -2447,7 +2447,7 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
         <v>9.4</v>
@@ -2465,7 +2465,7 @@
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
         <v>190</v>
@@ -2474,106 +2474,106 @@
         <v>19.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>170</v>
+        <v>310</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>16</v>
       </c>
       <c r="BC8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
         <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8" t="n">
         <v>7.6</v>
@@ -2582,29 +2582,29 @@
         <v>9</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2635,91 +2635,91 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
         <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
         <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
         <v>280</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
@@ -2728,7 +2728,7 @@
         <v>120</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>95</v>
@@ -2737,128 +2737,128 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO9" t="n">
         <v>22</v>
       </c>
-      <c r="AO9" t="n">
-        <v>26</v>
-      </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>16.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>17</v>
       </c>
-      <c r="BG9" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT9" t="n">
+      <c r="BU9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BX9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G10" t="n">
         <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2919,22 +2919,22 @@
         <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
         <v>1.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
         <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
         <v>1.26</v>
@@ -2970,7 +2970,7 @@
         <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -3003,10 +3003,10 @@
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -3018,7 +3018,7 @@
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -3030,7 +3030,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
         <v>17</v>
@@ -3042,7 +3042,7 @@
         <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
         <v>6.6</v>
@@ -3054,65 +3054,65 @@
         <v>4.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
         <v>12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR10" t="n">
         <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>1.21</v>
@@ -3167,34 +3167,34 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
         <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3203,16 +3203,16 @@
         <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD11" t="n">
         <v>60</v>
@@ -3221,19 +3221,19 @@
         <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
         <v>510</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>14</v>
@@ -3242,37 +3242,37 @@
         <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>40</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV11" t="n">
         <v>32</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
         <v>9.4</v>
@@ -3284,10 +3284,10 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
         <v>11.5</v>
@@ -3296,13 +3296,13 @@
         <v>22</v>
       </c>
       <c r="BE11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
         <v>5.7</v>
@@ -3311,10 +3311,10 @@
         <v>4.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,13 +3326,13 @@
         <v>4.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP11" t="n">
         <v>7</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
         <v>18.5</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -3433,16 +3433,16 @@
         <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3451,10 +3451,10 @@
         <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
@@ -3553,7 +3553,7 @@
         <v>26</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
         <v>25</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.26</v>
@@ -3696,28 +3696,28 @@
         <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
         <v>50</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
@@ -3726,13 +3726,13 @@
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>16</v>
@@ -3741,10 +3741,10 @@
         <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
         <v>44</v>
@@ -3753,7 +3753,7 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
         <v>23</v>
@@ -3762,13 +3762,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR13" t="n">
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
@@ -3798,7 +3798,7 @@
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
         <v>21</v>
@@ -3807,28 +3807,28 @@
         <v>15</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BJ13" t="n">
         <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
         <v>5.7</v>
@@ -3837,44 +3837,44 @@
         <v>4.6</v>
       </c>
       <c r="BP13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>14</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="CA13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3905,94 +3905,94 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AJ14" t="n">
         <v>70</v>
@@ -4001,22 +4001,22 @@
         <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -4028,7 +4028,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
         <v>9.800000000000001</v>
@@ -4043,92 +4043,92 @@
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BC14" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN14" t="n">
         <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>7</v>
       </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="BZ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CA14" t="n">
         <v>6.4</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
@@ -4183,10 +4183,10 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
         <v>2.6</v>
@@ -4195,7 +4195,7 @@
         <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
         <v>2.36</v>
@@ -4207,37 +4207,37 @@
         <v>2.66</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
         <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -4249,28 +4249,28 @@
         <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM15" t="n">
         <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP15" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -4279,19 +4279,19 @@
         <v>40</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
         <v>24</v>
       </c>
       <c r="AX15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
@@ -4306,7 +4306,7 @@
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>20</v>
@@ -4315,10 +4315,10 @@
         <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH15" t="n">
         <v>4.7</v>
@@ -4330,7 +4330,7 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,50 +4339,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BW15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA15" t="n">
         <v>6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -4428,7 +4428,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.34</v>
@@ -4440,28 +4440,28 @@
         <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
@@ -4470,22 +4470,22 @@
         <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
         <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -4494,7 +4494,7 @@
         <v>170</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AH16" t="n">
         <v>130</v>
@@ -4515,19 +4515,19 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AP16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS16" t="n">
         <v>7.4</v>
@@ -4539,7 +4539,7 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW16" t="n">
         <v>7.4</v>
@@ -4551,31 +4551,31 @@
         <v>16.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI16" t="n">
         <v>3.15</v>
@@ -4584,31 +4584,31 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.94</v>
+        <v>5.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="BT16" t="n">
         <v>4.5</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.68</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -4667,31 +4667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
@@ -4709,19 +4709,19 @@
         <v>1.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
@@ -4733,22 +4733,22 @@
         <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AE17" t="n">
         <v>320</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
@@ -4757,58 +4757,58 @@
         <v>150</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
         <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR17" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
         <v>6.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,16 +4817,16 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="n">
         <v>5.9</v>
@@ -4835,62 +4835,62 @@
         <v>4.3</v>
       </c>
       <c r="BJ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>9.6</v>
       </c>
-      <c r="BK17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CA17" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
         <v>2.34</v>
@@ -4933,7 +4933,7 @@
         <v>2.58</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -4954,7 +4954,7 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R18" t="n">
         <v>1.51</v>
@@ -4963,7 +4963,7 @@
         <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
         <v>2.38</v>
@@ -4972,7 +4972,7 @@
         <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
         <v>500</v>
@@ -5002,7 +5002,7 @@
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
         <v>60</v>
@@ -5044,7 +5044,7 @@
         <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
         <v>7</v>
@@ -5074,10 +5074,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
         <v>5.5</v>
@@ -5134,7 +5134,7 @@
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -5175,61 +5175,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
         <v>15</v>
@@ -5241,10 +5241,10 @@
         <v>90</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>18.5</v>
@@ -5259,10 +5259,10 @@
         <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
         <v>36</v>
@@ -5274,13 +5274,13 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
         <v>27</v>
       </c>
       <c r="AO19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
         <v>10.5</v>
@@ -5289,10 +5289,10 @@
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5310,67 +5310,67 @@
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ19" t="n">
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP19" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>13</v>
-      </c>
       <c r="BZ19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G20" t="n">
         <v>1.94</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
         <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -5459,10 +5459,10 @@
         <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
@@ -5489,7 +5489,7 @@
         <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AA20" t="n">
         <v>120</v>
@@ -5498,97 +5498,97 @@
         <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI20" t="n">
         <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AO20" t="n">
         <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>17</v>
       </c>
-      <c r="BA20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD20" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
@@ -5633,7 +5633,7 @@
         <v>6</v>
       </c>
       <c r="BV20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
         <v>11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
-        <v>16.5</v>
+        <v>240</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,28 +887,28 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>13.5</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -935,152 +935,152 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>5.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>470</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
-        <v>930</v>
+        <v>460</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="AM2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.16</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>11</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>100</v>
       </c>
       <c r="BB2" t="n">
         <v>5.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.92</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Skovde Aik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1.36</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>2.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>330</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>15</v>
       </c>
-      <c r="AT3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>18</v>
-      </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Skovde Aik</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="J4" t="n">
-        <v>3.95</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.54</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>100</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AV4" t="n">
         <v>11</v>
       </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>3</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>250</v>
       </c>
       <c r="BA4" t="n">
-        <v>17.5</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>250</v>
       </c>
       <c r="BD4" t="n">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>2.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>1.18</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="K5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S5" t="n">
+        <v>42</v>
+      </c>
+      <c r="T5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.51</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>1.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE5" t="n">
         <v>170</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
         <v>16</v>
       </c>
-      <c r="AC5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>120</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
         <v>4.7</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X6" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AM6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP6" t="n">
         <v>22</v>
       </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>300</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>2.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.84</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AD7" t="n">
+        <v>860</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH7" t="n">
         <v>22</v>
       </c>
-      <c r="Y7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17</v>
-      </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
         <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="AV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF7" t="n">
         <v>14</v>
       </c>
-      <c r="AW7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM8" t="n">
         <v>5.1</v>
       </c>
-      <c r="X8" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>520</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AN8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>16</v>
       </c>
-      <c r="AC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>1.92</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="K9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O9" t="n">
         <v>4.8</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.16</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="S9" t="n">
-        <v>2.26</v>
+        <v>120</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>2.36</v>
       </c>
       <c r="Y9" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>540</v>
       </c>
       <c r="AI9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AK9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>320</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>160</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>240</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>350</v>
+      </c>
+      <c r="BF9" t="n">
         <v>200</v>
       </c>
-      <c r="AN9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>260</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>2.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>1.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>5.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>40</v>
       </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>44</v>
-      </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>340</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>17.5</v>
+        <v>470</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AU10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BE10" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BG10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG10" t="n">
-        <v>14</v>
-      </c>
       <c r="BH10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>85</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>1.11</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>350</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>700</v>
+        <v>770</v>
       </c>
       <c r="AB11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>750</v>
       </c>
       <c r="AE11" t="n">
-        <v>700</v>
+        <v>990</v>
       </c>
       <c r="AF11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>870</v>
       </c>
       <c r="AI11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="AW11" t="n">
-        <v>36</v>
+        <v>3.15</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>1.23</v>
       </c>
       <c r="BB11" t="n">
         <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>10</v>
+        <v>1.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BZ11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO12" t="n">
         <v>4.3</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X12" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="BP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY12" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="BZ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA12" t="n">
         <v>11</v>
       </c>
-      <c r="AR12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,493 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
         <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN13" t="n">
         <v>15</v>
       </c>
-      <c r="Z13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AO13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BQ13" t="n">
         <v>7.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="CA13" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>10</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Universidad de Chile</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>OHiggins</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>140</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>27</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -860,16 +860,16 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.45</v>
@@ -887,13 +887,13 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
@@ -902,10 +902,10 @@
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.87</v>
@@ -926,19 +926,19 @@
         <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
         <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>19.5</v>
@@ -947,70 +947,70 @@
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
         <v>48</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
@@ -1019,68 +1019,68 @@
         <v>55</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL2" t="n">
         <v>150</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>120</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV2" t="n">
         <v>34</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BX2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BZ2" t="n">
         <v>32</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.93</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.97</v>
-      </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1138,52 +1138,52 @@
         <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
         <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
@@ -1192,7 +1192,7 @@
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
@@ -1207,19 +1207,19 @@
         <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
         <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -1231,31 +1231,31 @@
         <v>38</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
         <v>18.5</v>
@@ -1264,77 +1264,77 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>140</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX3" t="n">
         <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-18.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="I2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>4.3</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB2" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
         <v>60</v>
       </c>
-      <c r="AF2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="BE2" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF2" t="n">
         <v>25</v>
       </c>
-      <c r="AL2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>18</v>
-      </c>
       <c r="BG2" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="H3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.8</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
         <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3" t="n">
         <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK3" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AR3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AS3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
